--- a/templates/Anexo-II-A-Detalle-horas-KLG.xlsx
+++ b/templates/Anexo-II-A-Detalle-horas-KLG.xlsx
@@ -763,12 +763,10 @@
           <t>Horas en Kimai según C.UNIX</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n">
-        <v>306</v>
-      </c>
+      <c r="B5" s="8" t="n"/>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>Registros de Kimai al 29/09/2026. Coinciden día por día con las exportaciones enviadas por KLG.</t>
+          <t>C.UNIX anota aca el total que le da Kimai; la diferencia de abajo debe ser 0.</t>
         </is>
       </c>
     </row>
